--- a/files/제13회 영등포구 줄넘기대회 참가신청서(단체).xlsx
+++ b/files/제13회 영등포구 줄넘기대회 참가신청서(단체).xlsx
@@ -1048,7 +1048,7 @@
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>※ 보호자 동의여부를 포함한 단체 참여하는 과정에서의 책임 해당 단체에 있습니다. 이에 동의하고 대회에 참여합니다.</t>
+          <t>※ 보호자 동의여부를 포함한 단체 참여하는 과정에서의 책임은 해당 단체에 있습니다. 이에 동의하고 대회에 참여합니다.</t>
         </is>
       </c>
       <c r="C14" s="31" t="n"/>

--- a/files/제13회 영등포구 줄넘기대회 참가신청서(단체).xlsx
+++ b/files/제13회 영등포구 줄넘기대회 참가신청서(단체).xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -784,6 +784,7 @@
     <col width="78" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="36" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -791,6 +792,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -823,7 +825,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>유치부(7세), 초등부(1~6학년), 중등부(통합) · 전체 선착순 200명</t>
+          <t>유치부(7세), 초등부(1~6학년), 중등부(통합) · 전체 선착순 300명</t>
         </is>
       </c>
     </row>
@@ -944,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -952,6 +954,7 @@
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -959,6 +962,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
